--- a/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D525624A-3587-43AC-9D72-C1114B4FA967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A132479-70BD-4CB8-A242-8DD691D43D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="144">
   <si>
     <t>Client</t>
   </si>
@@ -473,6 +473,9 @@
   </si>
   <si>
     <t>Derek Janisch</t>
+  </si>
+  <si>
+    <t>Debtor Advisors</t>
   </si>
 </sst>
 </file>
@@ -522,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -536,6 +539,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -850,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
@@ -1062,6 +1066,104 @@
         <v>126</v>
       </c>
     </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
+        <v>139</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" t="s">
+        <v>126</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="R3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="U3" t="s">
+        <v>35</v>
+      </c>
+      <c r="V3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W3" t="s">
+        <v>37</v>
+      </c>
+      <c r="X3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1242,9 +1344,6 @@
       <c r="A5" t="s">
         <v>58</v>
       </c>
-      <c r="D5" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1463,26 +1562,26 @@
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="7" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="7" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="7" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1497,7 +1596,7 @@
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="7" t="s">
         <v>109</v>
       </c>
     </row>

--- a/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A132479-70BD-4CB8-A242-8DD691D43D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D669CB91-114B-4342-96CD-9A589275AB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -130,9 +130,6 @@
     <t>Techno Coatings, Inc.</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -476,6 +473,9 @@
   </si>
   <si>
     <t>Debtor Advisors</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -525,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -539,7 +539,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -558,9 +557,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -598,7 +597,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -704,7 +703,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -846,7 +845,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -947,7 +946,7 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>25</v>
@@ -956,16 +955,16 @@
         <v>26</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="AE1" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="AF1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
@@ -976,94 +975,94 @@
         <v>27</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" t="s">
+        <v>138</v>
+      </c>
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" t="s">
         <v>125</v>
       </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="O2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="R2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="U2" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" t="s">
-        <v>139</v>
-      </c>
-      <c r="L2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" t="s">
-        <v>126</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="R2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S2" t="s">
-        <v>34</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="U2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W2" t="s">
-        <v>37</v>
-      </c>
-      <c r="X2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>129</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>30</v>
-      </c>
       <c r="AE2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
@@ -1074,94 +1073,94 @@
         <v>27</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" t="s">
         <v>143</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>28</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>29</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" t="s">
         <v>30</v>
       </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L3" t="s">
         <v>31</v>
       </c>
-      <c r="I3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" t="s">
+        <v>125</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="P3" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="R3" t="s">
         <v>33</v>
       </c>
-      <c r="N3" t="s">
+      <c r="S3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="U3" t="s">
+        <v>34</v>
+      </c>
+      <c r="V3" t="s">
+        <v>35</v>
+      </c>
+      <c r="W3" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y3" t="s">
         <v>126</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="R3" t="s">
-        <v>34</v>
-      </c>
-      <c r="S3" t="s">
-        <v>34</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="U3" t="s">
-        <v>35</v>
-      </c>
-      <c r="V3" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3" t="s">
-        <v>37</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="Z3" t="s">
         <v>38</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AA3" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB3" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="Z3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AC3" t="s">
         <v>128</v>
       </c>
-      <c r="AC3" t="s">
-        <v>129</v>
-      </c>
       <c r="AD3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1180,18 +1179,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1206,12 +1205,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1226,12 +1225,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1246,54 +1245,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
         <v>50</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>51</v>
-      </c>
-      <c r="D2" t="s">
-        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1313,291 +1312,291 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
+      <c r="A47" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>109</v>
+      <c r="A53" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1616,21 +1615,21 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2">
         <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I2">
         <v>25</v>
@@ -1638,7 +1637,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B3">
         <v>65</v>
@@ -1659,17 +1658,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1688,26 +1687,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D669CB91-114B-4342-96CD-9A589275AB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D67570-BE51-46F2-B614-B88F8EBAB791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -445,9 +445,6 @@
     <t>Opportunities</t>
   </si>
   <si>
-    <t>William Peluchiwski</t>
-  </si>
-  <si>
     <t>FASJobType</t>
   </si>
   <si>
@@ -476,6 +473,9 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>Eric Winthrop</t>
   </si>
 </sst>
 </file>
@@ -946,7 +946,7 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>25</v>
@@ -955,13 +955,13 @@
         <v>26</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>39</v>
@@ -978,7 +978,7 @@
         <v>124</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -999,7 +999,7 @@
         <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L2" t="s">
         <v>31</v>
@@ -1011,13 +1011,13 @@
         <v>125</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R2" t="s">
         <v>33</v>
@@ -1026,7 +1026,7 @@
         <v>33</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="U2" t="s">
         <v>34</v>
@@ -1047,7 +1047,7 @@
         <v>38</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AB2" s="3" t="s">
         <v>127</v>
@@ -1073,10 +1073,10 @@
         <v>27</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" t="s">
         <v>142</v>
-      </c>
-      <c r="D3" t="s">
-        <v>143</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -1097,7 +1097,7 @@
         <v>29</v>
       </c>
       <c r="K3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L3" t="s">
         <v>31</v>
@@ -1109,13 +1109,13 @@
         <v>125</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R3" t="s">
         <v>33</v>
@@ -1124,7 +1124,7 @@
         <v>33</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="U3" t="s">
         <v>34</v>
@@ -1145,7 +1145,7 @@
         <v>38</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AB3" s="3" t="s">
         <v>127</v>
@@ -1173,7 +1173,7 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D67570-BE51-46F2-B614-B88F8EBAB791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00315E2C-9ABE-429F-B846-8BD9A82798EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="145">
   <si>
     <t>Client</t>
   </si>
@@ -385,9 +385,6 @@
     <t>Alex Lerer</t>
   </si>
   <si>
-    <t>Alex Maffei</t>
-  </si>
-  <si>
     <t>Alex Orlean</t>
   </si>
   <si>
@@ -409,9 +406,6 @@
     <t>Ali Amin</t>
   </si>
   <si>
-    <t>Alicia Furio</t>
-  </si>
-  <si>
     <t>Allen Plunk</t>
   </si>
   <si>
@@ -476,13 +470,22 @@
   </si>
   <si>
     <t>Eric Winthrop</t>
+  </si>
+  <si>
+    <t>Adriana Stacey</t>
+  </si>
+  <si>
+    <t>Ajay Arelli</t>
+  </si>
+  <si>
+    <t>Alberico Altieri</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,6 +503,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -525,7 +535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -539,6 +549,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -854,22 +865,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
   <dimension ref="A1:AF3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -946,7 +957,7 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>25</v>
@@ -955,19 +966,19 @@
         <v>26</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -975,10 +986,10 @@
         <v>27</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -999,7 +1010,7 @@
         <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L2" t="s">
         <v>31</v>
@@ -1008,16 +1019,16 @@
         <v>32</v>
       </c>
       <c r="N2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="R2" t="s">
         <v>33</v>
@@ -1026,7 +1037,7 @@
         <v>33</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="U2" t="s">
         <v>34</v>
@@ -1041,19 +1052,19 @@
         <v>37</v>
       </c>
       <c r="Y2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Z2" t="s">
         <v>38</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AC2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AD2" t="s">
         <v>29</v>
@@ -1062,10 +1073,10 @@
         <v>29</v>
       </c>
       <c r="AF2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1073,10 +1084,10 @@
         <v>27</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -1097,7 +1108,7 @@
         <v>29</v>
       </c>
       <c r="K3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L3" t="s">
         <v>31</v>
@@ -1106,16 +1117,16 @@
         <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="R3" t="s">
         <v>33</v>
@@ -1124,7 +1135,7 @@
         <v>33</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="U3" t="s">
         <v>34</v>
@@ -1139,19 +1150,19 @@
         <v>37</v>
       </c>
       <c r="Y3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Z3" t="s">
         <v>38</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AC3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AD3" t="s">
         <v>29</v>
@@ -1160,7 +1171,7 @@
         <v>29</v>
       </c>
       <c r="AF3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1171,13 +1182,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -1185,12 +1196,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1201,16 +1212,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86829626-F719-4BD0-AEC4-F096FBF467CD}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1221,16 +1232,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9CE0B9-361D-4D21-9EAF-7162B1BF1310}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1241,9 +1252,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -1269,7 +1280,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -1303,299 +1314,302 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>54</v>
       </c>
-      <c r="D2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>55</v>
       </c>
-      <c r="D3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>56</v>
       </c>
-      <c r="D4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>58</v>
       </c>
-      <c r="D6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>66</v>
       </c>
-      <c r="D14" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
         <v>108</v>
       </c>
     </row>
@@ -1607,13 +1621,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -1621,7 +1635,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -1635,7 +1649,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -1651,24 +1665,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1679,13 +1693,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="76.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="76.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>81</v>
       </c>
@@ -1693,20 +1707,20 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00315E2C-9ABE-429F-B846-8BD9A82798EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB2BAF5-E0AC-4667-BB25-546103894827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="147">
   <si>
     <t>Client</t>
   </si>
@@ -367,9 +367,6 @@
     <t>Alexander Garcia</t>
   </si>
   <si>
-    <t>Alexandra Lac</t>
-  </si>
-  <si>
     <t>Alex Cohen</t>
   </si>
   <si>
@@ -475,10 +472,19 @@
     <t>Adriana Stacey</t>
   </si>
   <si>
-    <t>Ajay Arelli</t>
-  </si>
-  <si>
-    <t>Alberico Altieri</t>
+    <t>Tanya Wong</t>
+  </si>
+  <si>
+    <t>Tim Green</t>
+  </si>
+  <si>
+    <t>Nick Li</t>
+  </si>
+  <si>
+    <t>Steven White</t>
+  </si>
+  <si>
+    <t>Vamsi Manda</t>
   </si>
 </sst>
 </file>
@@ -535,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -550,6 +556,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -865,22 +872,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
   <dimension ref="A1:AF3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -957,7 +964,7 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>25</v>
@@ -966,19 +973,19 @@
         <v>26</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -986,10 +993,10 @@
         <v>27</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -1010,7 +1017,7 @@
         <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L2" t="s">
         <v>31</v>
@@ -1019,16 +1026,16 @@
         <v>32</v>
       </c>
       <c r="N2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R2" t="s">
         <v>33</v>
@@ -1037,7 +1044,7 @@
         <v>33</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="U2" t="s">
         <v>34</v>
@@ -1052,19 +1059,19 @@
         <v>37</v>
       </c>
       <c r="Y2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z2" t="s">
         <v>38</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AB2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC2" t="s">
         <v>125</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>126</v>
       </c>
       <c r="AD2" t="s">
         <v>29</v>
@@ -1073,10 +1080,10 @@
         <v>29</v>
       </c>
       <c r="AF2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1084,10 +1091,10 @@
         <v>27</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" t="s">
         <v>139</v>
-      </c>
-      <c r="D3" t="s">
-        <v>140</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -1108,7 +1115,7 @@
         <v>29</v>
       </c>
       <c r="K3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L3" t="s">
         <v>31</v>
@@ -1117,16 +1124,16 @@
         <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R3" t="s">
         <v>33</v>
@@ -1135,7 +1142,7 @@
         <v>33</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="U3" t="s">
         <v>34</v>
@@ -1150,19 +1157,19 @@
         <v>37</v>
       </c>
       <c r="Y3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z3" t="s">
         <v>38</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AB3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC3" t="s">
         <v>125</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>126</v>
       </c>
       <c r="AD3" t="s">
         <v>29</v>
@@ -1171,7 +1178,7 @@
         <v>29</v>
       </c>
       <c r="AF3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1182,13 +1189,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -1196,12 +1203,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1212,16 +1219,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86829626-F719-4BD0-AEC4-F096FBF467CD}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1232,16 +1239,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9CE0B9-361D-4D21-9EAF-7162B1BF1310}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1252,9 +1259,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -1280,7 +1287,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -1314,303 +1321,303 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
-        <v>108</v>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="8" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1621,13 +1628,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -1635,7 +1642,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -1649,7 +1656,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -1665,24 +1672,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1693,13 +1700,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="76.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="76.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>81</v>
       </c>
@@ -1707,20 +1714,20 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB2BAF5-E0AC-4667-BB25-546103894827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A024AF3B-D677-453D-A7D0-9B9B64E752AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="148">
   <si>
     <t>Client</t>
   </si>
@@ -412,9 +412,6 @@
     <t>Creditor Advisors</t>
   </si>
   <si>
-    <t>Ayati Arvind</t>
-  </si>
-  <si>
     <t>FR</t>
   </si>
   <si>
@@ -485,6 +482,12 @@
   </si>
   <si>
     <t>Vamsi Manda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andy Chen </t>
+  </si>
+  <si>
+    <t>Andy Chen </t>
   </si>
 </sst>
 </file>
@@ -872,22 +875,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
   <dimension ref="A1:AF3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -964,7 +968,7 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>25</v>
@@ -973,19 +977,19 @@
         <v>26</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -996,7 +1000,7 @@
         <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -1017,7 +1021,7 @@
         <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L2" t="s">
         <v>31</v>
@@ -1026,16 +1030,16 @@
         <v>32</v>
       </c>
       <c r="N2" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R2" t="s">
         <v>33</v>
@@ -1044,7 +1048,7 @@
         <v>33</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="U2" t="s">
         <v>34</v>
@@ -1059,19 +1063,19 @@
         <v>37</v>
       </c>
       <c r="Y2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Z2" t="s">
         <v>38</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC2" t="s">
         <v>124</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>125</v>
       </c>
       <c r="AD2" t="s">
         <v>29</v>
@@ -1079,11 +1083,11 @@
       <c r="AE2" t="s">
         <v>29</v>
       </c>
-      <c r="AF2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF2" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1091,10 +1095,10 @@
         <v>27</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D3" t="s">
         <v>138</v>
-      </c>
-      <c r="D3" t="s">
-        <v>139</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -1115,7 +1119,7 @@
         <v>29</v>
       </c>
       <c r="K3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L3" t="s">
         <v>31</v>
@@ -1124,16 +1128,16 @@
         <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R3" t="s">
         <v>33</v>
@@ -1142,7 +1146,7 @@
         <v>33</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="U3" t="s">
         <v>34</v>
@@ -1157,19 +1161,19 @@
         <v>37</v>
       </c>
       <c r="Y3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Z3" t="s">
         <v>38</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC3" t="s">
         <v>124</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>125</v>
       </c>
       <c r="AD3" t="s">
         <v>29</v>
@@ -1177,8 +1181,8 @@
       <c r="AE3" t="s">
         <v>29</v>
       </c>
-      <c r="AF3" t="s">
-        <v>122</v>
+      <c r="AF3" s="8" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1189,13 +1193,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -1203,12 +1207,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1219,16 +1223,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86829626-F719-4BD0-AEC4-F096FBF467CD}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1239,16 +1243,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9CE0B9-361D-4D21-9EAF-7162B1BF1310}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1259,9 +1263,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -1287,7 +1291,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -1321,49 +1325,49 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>109</v>
       </c>
@@ -1371,7 +1375,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -1379,7 +1383,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -1387,7 +1391,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -1395,7 +1399,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>64</v>
       </c>
@@ -1403,62 +1407,62 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -1466,100 +1470,100 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>112</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>113</v>
       </c>
@@ -1567,47 +1571,47 @@
         <v>101</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>116</v>
       </c>
@@ -1615,8 +1619,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>107</v>
       </c>
     </row>
@@ -1628,13 +1632,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -1642,7 +1646,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -1656,7 +1660,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -1672,24 +1676,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1700,13 +1704,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="76.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="76.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>81</v>
       </c>
@@ -1714,7 +1718,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>83</v>
       </c>
@@ -1722,7 +1726,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>83</v>
       </c>

--- a/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A024AF3B-D677-453D-A7D0-9B9B64E752AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A501399A-4E5C-45CF-839E-C244017ABD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -1083,7 +1083,7 @@
       <c r="AE2" t="s">
         <v>29</v>
       </c>
-      <c r="AF2" s="8" t="s">
+      <c r="AF2" t="s">
         <v>147</v>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       <c r="AE3" t="s">
         <v>29</v>
       </c>
-      <c r="AF3" s="8" t="s">
+      <c r="AF3" t="s">
         <v>147</v>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="8" t="s">
         <v>110</v>
       </c>
       <c r="B11" s="7" t="s">

--- a/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A501399A-4E5C-45CF-839E-C244017ABD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB288037-CAB5-4ED0-AA94-0340C85BCF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -460,9 +457,6 @@
     <t>Debtor Advisors</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>Eric Winthrop</t>
   </si>
   <si>
@@ -488,6 +482,12 @@
   </si>
   <si>
     <t>Andy Chen </t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
   </si>
 </sst>
 </file>
@@ -544,7 +544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -559,7 +559,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -902,287 +901,287 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="AE1" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="AF1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" t="s">
+        <v>144</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="R2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="U2" t="s">
+        <v>33</v>
+      </c>
+      <c r="V2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y2" t="s">
         <v>121</v>
       </c>
-      <c r="D2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="Z2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD2" t="s">
         <v>28</v>
       </c>
-      <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>133</v>
-      </c>
-      <c r="L2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" t="s">
-        <v>146</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="R2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S2" t="s">
-        <v>33</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="U2" t="s">
-        <v>34</v>
-      </c>
-      <c r="V2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W2" t="s">
-        <v>36</v>
-      </c>
-      <c r="X2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>29</v>
-      </c>
       <c r="AE2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>28</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
+        <v>132</v>
+      </c>
+      <c r="L3" t="s">
         <v>30</v>
       </c>
-      <c r="I3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
+        <v>144</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="L3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="P3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="R3" t="s">
         <v>32</v>
       </c>
-      <c r="N3" t="s">
-        <v>146</v>
-      </c>
-      <c r="O3" s="3" t="s">
+      <c r="S3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="P3" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="U3" t="s">
         <v>33</v>
       </c>
-      <c r="S3" t="s">
-        <v>33</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>34</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>35</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>36</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z3" t="s">
         <v>37</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AA3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB3" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="Z3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AC3" t="s">
         <v>123</v>
       </c>
-      <c r="AC3" t="s">
-        <v>124</v>
-      </c>
       <c r="AD3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1201,18 +1200,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1227,12 +1226,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1247,12 +1246,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1267,54 +1266,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>50</v>
-      </c>
-      <c r="D2" t="s">
-        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1334,294 +1333,294 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="D10" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1640,21 +1639,21 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2">
         <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I2">
         <v>25</v>
@@ -1662,7 +1661,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3">
         <v>65</v>
@@ -1683,17 +1682,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1712,26 +1711,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB288037-CAB5-4ED0-AA94-0340C85BCF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C3D370-6512-42FB-9B53-649C903C56A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -487,7 +487,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -874,23 +874,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
   <dimension ref="A1:AF3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -988,7 +988,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1192,13 +1192,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>137</v>
       </c>
@@ -1222,14 +1222,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86829626-F719-4BD0-AEC4-F096FBF467CD}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -1242,14 +1242,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9CE0B9-361D-4D21-9EAF-7162B1BF1310}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>127</v>
       </c>
@@ -1262,9 +1262,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>40</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -1324,49 +1324,49 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>109</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -1406,62 +1406,62 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>110</v>
       </c>
@@ -1469,67 +1469,67 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>111</v>
       </c>
@@ -1537,32 +1537,32 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>112</v>
       </c>
@@ -1570,47 +1570,47 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>106</v>
       </c>
@@ -1631,13 +1631,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>85</v>
       </c>
@@ -1675,22 +1675,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>143</v>
       </c>
@@ -1703,13 +1703,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="76.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="76.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>80</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>82</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>82</v>
       </c>

--- a/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTT0035666_VerifyInternalDealTeamForAnalystRoleLimitForFRLOBOpportunityEngagement.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41483088-61D1-4CC4-B5CD-5DF284448111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010A3413-F189-42EA-A23A-311BB745AD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
-    <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
-    <sheet name="Users" sheetId="2" r:id="rId2"/>
-    <sheet name="AppName" sheetId="8" r:id="rId3"/>
-    <sheet name="ModuleName" sheetId="9" r:id="rId4"/>
+    <sheet name="Users" sheetId="2" r:id="rId1"/>
+    <sheet name="AppName" sheetId="8" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="9" r:id="rId3"/>
+    <sheet name="AddOpportunity" sheetId="1" r:id="rId4"/>
     <sheet name="AddContact" sheetId="3" r:id="rId5"/>
     <sheet name="OppDealTeamMembers" sheetId="4" r:id="rId6"/>
     <sheet name="Roles" sheetId="7" r:id="rId7"/>
@@ -869,316 +869,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
-  <dimension ref="A1:AF3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" t="s">
-        <v>131</v>
-      </c>
-      <c r="L2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" t="s">
-        <v>143</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="R2" t="s">
-        <v>32</v>
-      </c>
-      <c r="S2" t="s">
-        <v>32</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="U2" t="s">
-        <v>33</v>
-      </c>
-      <c r="V2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" t="s">
-        <v>131</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" t="s">
-        <v>143</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="R3" t="s">
-        <v>32</v>
-      </c>
-      <c r="S3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="U3" t="s">
-        <v>33</v>
-      </c>
-      <c r="V3" t="s">
-        <v>34</v>
-      </c>
-      <c r="W3" t="s">
-        <v>35</v>
-      </c>
-      <c r="X3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1187,28 +899,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86829626-F719-4BD0-AEC4-F096FBF467CD}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1217,18 +919,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86829626-F719-4BD0-AEC4-F096FBF467CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9CE0B9-361D-4D21-9EAF-7162B1BF1310}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1237,18 +939,316 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9CE0B9-361D-4D21-9EAF-7162B1BF1310}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A698FC-E7B6-4C83-A074-4EAE7093E960}">
+  <dimension ref="A1:AF3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" t="s">
+        <v>131</v>
+      </c>
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" t="s">
+        <v>143</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="R2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="U2" t="s">
+        <v>33</v>
+      </c>
+      <c r="V2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
+        <v>131</v>
+      </c>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s">
+        <v>143</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="R3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="U3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V3" t="s">
+        <v>34</v>
+      </c>
+      <c r="W3" t="s">
+        <v>35</v>
+      </c>
+      <c r="X3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -1259,9 +1259,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>40</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -1321,49 +1321,49 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>109</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -1403,62 +1403,62 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>110</v>
       </c>
@@ -1466,67 +1466,67 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>111</v>
       </c>
@@ -1534,32 +1534,32 @@
         <v>137</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>112</v>
       </c>
@@ -1567,47 +1567,47 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>142</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>106</v>
       </c>
@@ -1628,13 +1628,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C94118-6319-40E3-9C0E-6605217BB92A}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>85</v>
       </c>
@@ -1672,22 +1672,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>142</v>
       </c>
@@ -1700,13 +1700,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="76.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="76.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>80</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>82</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>82</v>
       </c>
